--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192464</v>
+        <v>121192489</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>94572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577678</v>
+        <v>577675</v>
       </c>
       <c r="R2" t="n">
-        <v>6446559</v>
+        <v>6446609</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192402</v>
+        <v>121192464</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577720</v>
+        <v>577678</v>
       </c>
       <c r="R3" t="n">
-        <v>6446508</v>
+        <v>6446559</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192489</v>
+        <v>121192402</v>
       </c>
       <c r="B4" t="n">
-        <v>94562</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577675</v>
+        <v>577720</v>
       </c>
       <c r="R4" t="n">
-        <v>6446609</v>
+        <v>6446508</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192489</v>
+        <v>121192464</v>
       </c>
       <c r="B2" t="n">
-        <v>94572</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577675</v>
+        <v>577678</v>
       </c>
       <c r="R2" t="n">
-        <v>6446609</v>
+        <v>6446559</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192464</v>
+        <v>121192402</v>
       </c>
       <c r="B3" t="n">
         <v>100347</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577678</v>
+        <v>577720</v>
       </c>
       <c r="R3" t="n">
-        <v>6446559</v>
+        <v>6446508</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192402</v>
+        <v>121192489</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>94572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577720</v>
+        <v>577675</v>
       </c>
       <c r="R4" t="n">
-        <v>6446508</v>
+        <v>6446609</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192464</v>
+        <v>121192489</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>94584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577678</v>
+        <v>577675</v>
       </c>
       <c r="R2" t="n">
-        <v>6446559</v>
+        <v>6446609</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -780,7 +780,7 @@
         <v>121192402</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192489</v>
+        <v>121192464</v>
       </c>
       <c r="B4" t="n">
-        <v>94572</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577675</v>
+        <v>577678</v>
       </c>
       <c r="R4" t="n">
-        <v>6446609</v>
+        <v>6446559</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192489</v>
+        <v>121192402</v>
       </c>
       <c r="B2" t="n">
-        <v>94584</v>
+        <v>100361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577675</v>
+        <v>577720</v>
       </c>
       <c r="R2" t="n">
-        <v>6446609</v>
+        <v>6446508</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192402</v>
+        <v>121192464</v>
       </c>
       <c r="B3" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577720</v>
+        <v>577678</v>
       </c>
       <c r="R3" t="n">
-        <v>6446508</v>
+        <v>6446559</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192464</v>
+        <v>121192489</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>94585</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577678</v>
+        <v>577675</v>
       </c>
       <c r="R4" t="n">
-        <v>6446559</v>
+        <v>6446609</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192402</v>
+        <v>121192489</v>
       </c>
       <c r="B2" t="n">
-        <v>100361</v>
+        <v>94588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577720</v>
+        <v>577675</v>
       </c>
       <c r="R2" t="n">
-        <v>6446508</v>
+        <v>6446609</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192464</v>
+        <v>121192402</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577678</v>
+        <v>577720</v>
       </c>
       <c r="R3" t="n">
-        <v>6446559</v>
+        <v>6446508</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192489</v>
+        <v>121192464</v>
       </c>
       <c r="B4" t="n">
-        <v>94585</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577675</v>
+        <v>577678</v>
       </c>
       <c r="R4" t="n">
-        <v>6446609</v>
+        <v>6446559</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192489</v>
+        <v>121192402</v>
       </c>
       <c r="B2" t="n">
-        <v>94588</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577675</v>
+        <v>577720</v>
       </c>
       <c r="R2" t="n">
-        <v>6446609</v>
+        <v>6446508</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192402</v>
+        <v>121192489</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>94588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577720</v>
+        <v>577675</v>
       </c>
       <c r="R3" t="n">
-        <v>6446508</v>
+        <v>6446609</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192402</v>
+        <v>121192464</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577720</v>
+        <v>577678</v>
       </c>
       <c r="R2" t="n">
-        <v>6446508</v>
+        <v>6446559</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121192489</v>
       </c>
       <c r="B3" t="n">
-        <v>94588</v>
+        <v>94594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192464</v>
+        <v>121192402</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577678</v>
+        <v>577720</v>
       </c>
       <c r="R4" t="n">
-        <v>6446559</v>
+        <v>6446508</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 42463-2024 artfynd.xlsx
+++ b/artfynd/A 42463-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192464</v>
+        <v>121192402</v>
       </c>
       <c r="B2" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577678</v>
+        <v>577720</v>
       </c>
       <c r="R2" t="n">
-        <v>6446559</v>
+        <v>6446508</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192489</v>
+        <v>121192464</v>
       </c>
       <c r="B3" t="n">
-        <v>94594</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577675</v>
+        <v>577678</v>
       </c>
       <c r="R3" t="n">
-        <v>6446609</v>
+        <v>6446559</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192402</v>
+        <v>121192489</v>
       </c>
       <c r="B4" t="n">
-        <v>100370</v>
+        <v>94595</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577720</v>
+        <v>577675</v>
       </c>
       <c r="R4" t="n">
-        <v>6446508</v>
+        <v>6446609</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
